--- a/Modules/Nucleus/Nucleus_BOM.xlsx
+++ b/Modules/Nucleus/Nucleus_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\Nucleus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CAC9D2-65A2-4EA0-BBDF-D78EB8AC805A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31599BE5-5E21-485B-896F-F2A8B89F617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -401,9 +401,6 @@
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>https://www.ebay.co.uk/itm/185419609093</t>
   </si>
   <si>
@@ -610,9 +607,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/b3x8_bn7/bolts/bossard/1006614/</t>
   </si>
   <si>
@@ -1093,6 +1087,12 @@
   </si>
   <si>
     <t>https://www.buerklin.com/en/p/vishay/wirewound-resistors/mba02040c1203fct00/14E715/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -2130,7 +2130,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -2153,7 +2153,7 @@
         <v>114</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -2164,16 +2164,16 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>59</v>
@@ -2187,16 +2187,16 @@
         <v>220</v>
       </c>
       <c r="C4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>59</v>
@@ -2210,16 +2210,16 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>59</v>
@@ -2233,16 +2233,16 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>59</v>
@@ -2256,10 +2256,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E7" t="s">
         <v>29</v>
@@ -2268,7 +2268,7 @@
         <v>59</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -2279,7 +2279,7 @@
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>28</v>
@@ -2288,7 +2288,7 @@
         <v>29</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>59</v>
@@ -2311,10 +2311,10 @@
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -2325,19 +2325,19 @@
         <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -2348,19 +2348,19 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -2371,19 +2371,19 @@
         <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>35</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J12" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -2394,19 +2394,19 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
         <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2426,10 +2426,10 @@
         <v>40</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2443,16 +2443,16 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
         <v>41</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J15" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2466,13 +2466,13 @@
         <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E16" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>60</v>
@@ -2489,13 +2489,13 @@
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E17" t="s">
         <v>55</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>60</v>
@@ -2506,22 +2506,22 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2535,16 +2535,16 @@
         <v>52</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
         <v>49</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2564,10 +2564,10 @@
         <v>48</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2587,10 +2587,10 @@
         <v>20</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J21" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2610,10 +2610,10 @@
         <v>50</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2624,7 +2624,7 @@
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>44</v>
@@ -2633,10 +2633,10 @@
         <v>109</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2650,16 +2650,16 @@
         <v>42</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
         <v>120</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2670,7 +2670,7 @@
         <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>30</v>
@@ -2682,7 +2682,7 @@
         <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2690,13 +2690,13 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" t="s">
         <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E26" t="s">
         <v>23</v>
@@ -2705,7 +2705,7 @@
         <v>63</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2725,10 +2725,10 @@
         <v>24</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J27" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2742,13 +2742,13 @@
         <v>64</v>
       </c>
       <c r="D28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>113</v>
@@ -2771,10 +2771,10 @@
         <v>24</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J29" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2794,10 +2794,10 @@
         <v>24</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J30" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2817,10 +2817,10 @@
         <v>24</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="J31" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2840,7 +2840,7 @@
         <v>73</v>
       </c>
       <c r="J33" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2860,7 +2860,7 @@
         <v>77</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2880,7 +2880,7 @@
         <v>81</v>
       </c>
       <c r="J35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2897,10 +2897,10 @@
         <v>90</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2917,10 +2917,10 @@
         <v>91</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2937,10 +2937,10 @@
         <v>93</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J38" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2960,10 +2960,10 @@
         <v>110</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2980,10 +2980,10 @@
         <v>102</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="J41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -3000,10 +3000,10 @@
         <v>102</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J42" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
@@ -3020,10 +3020,10 @@
         <v>102</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J43" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -3034,16 +3034,16 @@
         <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
         <v>116</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
@@ -3078,10 +3078,10 @@
         <v>108</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="J47" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
@@ -3098,10 +3098,10 @@
         <v>85</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J48" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -3109,19 +3109,19 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
         <v>82</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J49" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -3135,10 +3135,10 @@
         <v>105</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -3146,46 +3146,46 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" t="s">
         <v>104</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B54" s="8" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B56" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B57" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B58" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B59" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B60" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3204,10 +3204,10 @@
         <v>117</v>
       </c>
       <c r="L63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O63" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="O63" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3221,10 +3221,10 @@
         <v>118</v>
       </c>
       <c r="L64" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O64" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="O64" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -3238,18 +3238,18 @@
         <v>119</v>
       </c>
       <c r="L65" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="O65" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="O65" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B67" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3284,34 +3284,34 @@
     <hyperlink ref="F40" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
     <hyperlink ref="J28" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
     <hyperlink ref="F44" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="F47" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="J52" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="F52" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="J51" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="F51" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="O63" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="O64" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="O65" r:id="rId38" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="J3" r:id="rId39" xr:uid="{DD0C5450-CE7D-49B7-8A3D-BBCECC2ABEC5}"/>
-    <hyperlink ref="F18" r:id="rId40" xr:uid="{940EE9BC-3C2B-4660-9EEC-D5A03BCC54A3}"/>
-    <hyperlink ref="F19" r:id="rId41" xr:uid="{38F3C576-E9F4-4E09-ADFC-99DBEE708395}"/>
-    <hyperlink ref="F27" r:id="rId42" xr:uid="{13CDBD9F-609D-4DBD-97BE-822003C4B835}"/>
-    <hyperlink ref="F29" r:id="rId43" xr:uid="{18F71FC3-BB9D-4329-A570-6693B623435A}"/>
-    <hyperlink ref="F30" r:id="rId44" xr:uid="{7FBCA6ED-A9F0-4C0E-BDD4-980D2C9B7AEC}"/>
-    <hyperlink ref="F31" r:id="rId45" xr:uid="{0A7E4D8D-669F-4DF0-965E-6BED00A668C1}"/>
-    <hyperlink ref="F49" r:id="rId46" xr:uid="{C637B40B-75E7-4AD6-9CA4-5BD086BF954E}"/>
-    <hyperlink ref="F23" r:id="rId47" xr:uid="{78D2B6DC-3673-4D93-8128-FA4E104975E9}"/>
-    <hyperlink ref="F48" r:id="rId48" xr:uid="{E476E4F0-7231-4718-8317-0FB8C00D41FB}"/>
-    <hyperlink ref="F12" r:id="rId49" xr:uid="{C840F209-F481-4A06-82A4-7E5214D75CF5}"/>
-    <hyperlink ref="F3" r:id="rId50" xr:uid="{EF5C823F-683E-4A42-9C85-853A7F3FF3BF}"/>
-    <hyperlink ref="F4" r:id="rId51" xr:uid="{08EBC80F-6A81-4437-AD19-7FBAB665B673}"/>
-    <hyperlink ref="F5" r:id="rId52" xr:uid="{A9BE85AF-F329-4FBA-A078-5F5653BE8366}"/>
-    <hyperlink ref="F6" r:id="rId53" xr:uid="{59009F66-7EEA-4B03-A562-D01C4E12B03F}"/>
-    <hyperlink ref="F8" r:id="rId54" xr:uid="{59EB1040-5ECC-475A-874F-4B6CDE5E9C70}"/>
-    <hyperlink ref="F17" r:id="rId55" xr:uid="{CCF82918-65AD-44A0-8EDB-02B9CF3FC458}"/>
-    <hyperlink ref="F16" r:id="rId56" xr:uid="{124C15F8-1F72-461A-999D-758BE781668B}"/>
-    <hyperlink ref="F28" r:id="rId57" xr:uid="{4F23CE7F-07D3-4328-AB2C-2287284D6781}"/>
-    <hyperlink ref="J7" r:id="rId58" xr:uid="{F8B8EE7C-13DB-4DD4-8922-5CCF2230580C}"/>
+    <hyperlink ref="J52" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="F52" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="J51" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="F51" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="O63" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="O64" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="O65" r:id="rId37" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="J3" r:id="rId38" xr:uid="{DD0C5450-CE7D-49B7-8A3D-BBCECC2ABEC5}"/>
+    <hyperlink ref="F18" r:id="rId39" xr:uid="{940EE9BC-3C2B-4660-9EEC-D5A03BCC54A3}"/>
+    <hyperlink ref="F19" r:id="rId40" xr:uid="{38F3C576-E9F4-4E09-ADFC-99DBEE708395}"/>
+    <hyperlink ref="F27" r:id="rId41" xr:uid="{13CDBD9F-609D-4DBD-97BE-822003C4B835}"/>
+    <hyperlink ref="F29" r:id="rId42" xr:uid="{18F71FC3-BB9D-4329-A570-6693B623435A}"/>
+    <hyperlink ref="F30" r:id="rId43" xr:uid="{7FBCA6ED-A9F0-4C0E-BDD4-980D2C9B7AEC}"/>
+    <hyperlink ref="F49" r:id="rId44" xr:uid="{C637B40B-75E7-4AD6-9CA4-5BD086BF954E}"/>
+    <hyperlink ref="F23" r:id="rId45" xr:uid="{78D2B6DC-3673-4D93-8128-FA4E104975E9}"/>
+    <hyperlink ref="F48" r:id="rId46" xr:uid="{E476E4F0-7231-4718-8317-0FB8C00D41FB}"/>
+    <hyperlink ref="F12" r:id="rId47" xr:uid="{C840F209-F481-4A06-82A4-7E5214D75CF5}"/>
+    <hyperlink ref="F3" r:id="rId48" xr:uid="{EF5C823F-683E-4A42-9C85-853A7F3FF3BF}"/>
+    <hyperlink ref="F4" r:id="rId49" xr:uid="{08EBC80F-6A81-4437-AD19-7FBAB665B673}"/>
+    <hyperlink ref="F5" r:id="rId50" xr:uid="{A9BE85AF-F329-4FBA-A078-5F5653BE8366}"/>
+    <hyperlink ref="F6" r:id="rId51" xr:uid="{59009F66-7EEA-4B03-A562-D01C4E12B03F}"/>
+    <hyperlink ref="F8" r:id="rId52" xr:uid="{59EB1040-5ECC-475A-874F-4B6CDE5E9C70}"/>
+    <hyperlink ref="F17" r:id="rId53" xr:uid="{CCF82918-65AD-44A0-8EDB-02B9CF3FC458}"/>
+    <hyperlink ref="F16" r:id="rId54" xr:uid="{124C15F8-1F72-461A-999D-758BE781668B}"/>
+    <hyperlink ref="F28" r:id="rId55" xr:uid="{4F23CE7F-07D3-4328-AB2C-2287284D6781}"/>
+    <hyperlink ref="J7" r:id="rId56" xr:uid="{F8B8EE7C-13DB-4DD4-8922-5CCF2230580C}"/>
+    <hyperlink ref="F31" r:id="rId57" xr:uid="{AEF2A778-B72E-4278-9BED-52672FDF6119}"/>
+    <hyperlink ref="F47" r:id="rId58" xr:uid="{C9E3C72A-8138-4360-BBE8-A56BD4C01EFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
